--- a/artfynd/A 62846-2023 artfynd.xlsx
+++ b/artfynd/A 62846-2023 artfynd.xlsx
@@ -2002,7 +2002,7 @@
         <v>110212427</v>
       </c>
       <c r="B13" t="n">
-        <v>5179</v>
+        <v>5182</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         <v>110212445</v>
       </c>
       <c r="B14" t="n">
-        <v>5179</v>
+        <v>5182</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 62846-2023 artfynd.xlsx
+++ b/artfynd/A 62846-2023 artfynd.xlsx
@@ -2002,7 +2002,7 @@
         <v>110212427</v>
       </c>
       <c r="B13" t="n">
-        <v>5182</v>
+        <v>5188</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         <v>110212445</v>
       </c>
       <c r="B14" t="n">
-        <v>5182</v>
+        <v>5188</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
